--- a/artfynd/A 60829-2025 artfynd.xlsx
+++ b/artfynd/A 60829-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,60 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91729505</v>
+        <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>57794</v>
+        <v>93083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102621</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stenvreten, Trösken, Upl</t>
+          <t>Stenvreten, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630125</v>
+        <v>630191</v>
       </c>
       <c r="R2" t="n">
-        <v>6725112</v>
+        <v>6725115</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>07:15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>07:15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,24 +765,367 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Moberg</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Moberg</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136830597</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136830697</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93447</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stenvreten, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>630194</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6725142</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830697</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>91729505</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57794</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stenvreten, Trösken, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>630125</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6725112</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-03-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-03-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jan Moberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jan Moberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/91729505</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136830633</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102479</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stenvreten, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>630212</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6725111</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830633</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60829-2025 artfynd.xlsx
+++ b/artfynd/A 60829-2025 artfynd.xlsx
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>630194</v>
+        <v>630189</v>
       </c>
       <c r="R3" t="n">
-        <v>6725142</v>
+        <v>6725131</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 60829-2025 artfynd.xlsx
+++ b/artfynd/A 60829-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136830633</v>
       </c>
       <c r="B5" t="n">
-        <v>102479</v>
+        <v>102485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60829-2025 artfynd.xlsx
+++ b/artfynd/A 60829-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136830633</v>
       </c>
       <c r="B5" t="n">
-        <v>102485</v>
+        <v>102487</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60829-2025 artfynd.xlsx
+++ b/artfynd/A 60829-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136830633</v>
       </c>
       <c r="B5" t="n">
-        <v>102487</v>
+        <v>102488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60829-2025 artfynd.xlsx
+++ b/artfynd/A 60829-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136830633</v>
       </c>
       <c r="B5" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60829-2025 artfynd.xlsx
+++ b/artfynd/A 60829-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136830633</v>
       </c>
       <c r="B5" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60829-2025 artfynd.xlsx
+++ b/artfynd/A 60829-2025 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>136830633</v>
       </c>
       <c r="B5" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60829-2025 artfynd.xlsx
+++ b/artfynd/A 60829-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136830633</v>
       </c>
       <c r="B5" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60829-2025 artfynd.xlsx
+++ b/artfynd/A 60829-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136830633</v>
       </c>
       <c r="B5" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60829-2025 artfynd.xlsx
+++ b/artfynd/A 60829-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136830633</v>
       </c>
       <c r="B5" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60829-2025 artfynd.xlsx
+++ b/artfynd/A 60829-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136830633</v>
       </c>
       <c r="B5" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60829-2025 artfynd.xlsx
+++ b/artfynd/A 60829-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136830633</v>
       </c>
       <c r="B5" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60829-2025 artfynd.xlsx
+++ b/artfynd/A 60829-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136830633</v>
       </c>
       <c r="B5" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60829-2025 artfynd.xlsx
+++ b/artfynd/A 60829-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136830633</v>
       </c>
       <c r="B5" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60829-2025 artfynd.xlsx
+++ b/artfynd/A 60829-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136830633</v>
       </c>
       <c r="B5" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60829-2025 artfynd.xlsx
+++ b/artfynd/A 60829-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136830633</v>
       </c>
       <c r="B5" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60829-2025 artfynd.xlsx
+++ b/artfynd/A 60829-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136830633</v>
       </c>
       <c r="B5" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60829-2025 artfynd.xlsx
+++ b/artfynd/A 60829-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60829-2025 artfynd.xlsx
+++ b/artfynd/A 60829-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
